--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2018_la_araucania.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -669,13 +669,13 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         <v>32</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="10">
@@ -718,10 +718,10 @@
         <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -738,13 +738,13 @@
         <v>32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="12">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2018_la_araucania.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:38</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2018_la_araucania.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
